--- a/Server.Solution/Server.Api/Archives/expenses.xlsx
+++ b/Server.Solution/Server.Api/Archives/expenses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sysdba\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sysdba\Desktop\Junho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{EEF0EC81-6FF9-446B-A994-9866C10255F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808DF0F8-EB08-4962-82E8-64CE7B352B3E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-135" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXPENSES" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="149">
   <si>
     <t>EUFLAZIO BIGOTO</t>
   </si>
@@ -115,18 +115,12 @@
     <t>COMACO</t>
   </si>
   <si>
-    <t>CASA-MT CONSTRUÇÃO</t>
-  </si>
-  <si>
     <t>COMERCIAL SANDR</t>
   </si>
   <si>
     <t>VIVO FIXO NACIONAL</t>
   </si>
   <si>
-    <t>CASA-TELEFONE</t>
-  </si>
-  <si>
     <t>ADRIANO</t>
   </si>
   <si>
@@ -277,24 +271,15 @@
     <t>Aplicação Poupança</t>
   </si>
   <si>
-    <t>XXX</t>
-  </si>
-  <si>
     <t>Benefício INSS</t>
   </si>
   <si>
     <t>S A L D O</t>
   </si>
   <si>
-    <t>Saldo Anterior</t>
-  </si>
-  <si>
     <t>Transferência</t>
   </si>
   <si>
-    <t>BENEFÍCIO INSS</t>
-  </si>
-  <si>
     <t>SALDO ANTERIOR</t>
   </si>
   <si>
@@ -316,9 +301,6 @@
     <t>IDENTICA CORR DE SEG LTD</t>
   </si>
   <si>
-    <t>BB RF REF DI PLUS ÁGIL</t>
-  </si>
-  <si>
     <t>MARIMEL</t>
   </si>
   <si>
@@ -340,9 +322,6 @@
     <t>BENEFICIO INSS</t>
   </si>
   <si>
-    <t>PAGAMENTO DE VOLETO - NU PAGAMENTOS SA</t>
-  </si>
-  <si>
     <t>ORIGEM</t>
   </si>
   <si>
@@ -382,9 +361,6 @@
     <t>A PAULISTINHA</t>
   </si>
   <si>
-    <t>MT CONSTRUÇÃO</t>
-  </si>
-  <si>
     <t>RICARDO</t>
   </si>
   <si>
@@ -436,13 +412,67 @@
     <t>APLICAÇÃO</t>
   </si>
   <si>
-    <t>CRÉDITO</t>
+    <t>MOVIMENTACAO INTERNA</t>
+  </si>
+  <si>
+    <t>CREDITO</t>
+  </si>
+  <si>
+    <t>PAGAMENTO DE BOLETO - NU PAGAMENTOS SA</t>
+  </si>
+  <si>
+    <t>AJUSTE DE SALDO</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA ENTRE CONTAS</t>
+  </si>
+  <si>
+    <t>INVESTIMENTO</t>
+  </si>
+  <si>
+    <t>ESTORNO/DEVOLUCAO</t>
+  </si>
+  <si>
+    <t>MT CONSTRUCAO</t>
+  </si>
+  <si>
+    <t>Rrfcomerciode</t>
+  </si>
+  <si>
+    <t>Ultraforte</t>
+  </si>
+  <si>
+    <t>Pix - Recebido</t>
+  </si>
+  <si>
+    <t>Aldarrestaurante</t>
+  </si>
+  <si>
+    <t>RESTAURANTE</t>
+  </si>
+  <si>
+    <t>Sbm Espetos</t>
+  </si>
+  <si>
+    <t>LANCHE</t>
+  </si>
+  <si>
+    <t>Pagamento recebido</t>
+  </si>
+  <si>
+    <t>Juliano de Lima Simoe</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
+    <t>Operações na Cetip</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -926,7 +956,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -935,6 +965,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1289,24 +1320,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C99"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="3" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1354,105 +1385,105 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>17</v>
@@ -1460,26 +1491,26 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>17</v>
@@ -1487,7 +1518,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
@@ -1495,7 +1526,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>17</v>
@@ -1503,32 +1534,35 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1539,12 +1573,12 @@
         <v>17</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>17</v>
@@ -1552,18 +1586,18 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="3">
-        <v>1.99</v>
+      <c r="C28" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>17</v>
@@ -1574,640 +1608,691 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>17</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1.99</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1.99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>40</v>
+        <v>131</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>40</v>
+        <v>131</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>40</v>
+        <v>131</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>45</v>
+      <c r="A39" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>40</v>
+        <v>131</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>40</v>
+        <v>118</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>71</v>
+        <v>130</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>72</v>
+        <v>130</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>85</v>
+        <v>12</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>85</v>
+        <v>123</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>71</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>76</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>78</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>80</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C102">
-    <sortCondition ref="B43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C103">
+    <sortCondition ref="B1"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>